--- a/registration.xlsx
+++ b/registration.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1167,6 +1167,96 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>vinay</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>saidulu</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Western</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>5 months</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2025-12-23 17:33:58</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>veesamvinaykumar@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>nandhu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>charan</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Western</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>3 month</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2025-12-23 17:51:18</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>veesamvinaykumar@gmail.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
